--- a/docs/Uniconta_Labels_Standard.xlsx
+++ b/docs/Uniconta_Labels_Standard.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eilersenelectric-my.sharepoint.com/personal/vnn_eilersen_com/Documents/Dokumenter/Uniconta-PowerBI/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{8EB699F8-8285-4BA6-8132-DDF010203B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14FF34FC-577D-4780-9232-0F84C5EFA260}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{8EB699F8-8285-4BA6-8132-DDF010203B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6CEAF3E-9A87-4DFC-AB0A-CE6B7B569DEA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F0344905-1353-4E0D-BF0B-013AC37D91E4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Labels" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/docs/Uniconta_Labels_Standard.xlsx
+++ b/docs/Uniconta_Labels_Standard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eilersenelectric-my.sharepoint.com/personal/vnn_eilersen_com/Documents/Dokumenter/Uniconta-PowerBI/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{8EB699F8-8285-4BA6-8132-DDF010203B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6CEAF3E-9A87-4DFC-AB0A-CE6B7B569DEA}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{8EB699F8-8285-4BA6-8132-DDF010203B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC1E1BC5-3E7A-48CA-A71A-F730FA23F92F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F0344905-1353-4E0D-BF0B-013AC37D91E4}"/>
+    <workbookView xWindow="-15300" yWindow="465" windowWidth="10875" windowHeight="19095" xr2:uid="{F0344905-1353-4E0D-BF0B-013AC37D91E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21600,13 +21600,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -21629,8 +21635,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -21969,10 +21976,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EFAF229-A414-467E-84C5-BEDDBA48671D}">
-  <dimension ref="A1:B3718"/>
+  <dimension ref="A1:B3750"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="81" customWidth="1"/>
+    <col min="1" max="1" width="43.28515625" customWidth="1"/>
     <col min="2" max="2" width="75.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -51717,6 +51724,102 @@
         <v>7183</v>
       </c>
     </row>
+    <row r="3719" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3719" s="1"/>
+    </row>
+    <row r="3720" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3720" s="1"/>
+    </row>
+    <row r="3721" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3721" s="1"/>
+    </row>
+    <row r="3722" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3722" s="1"/>
+    </row>
+    <row r="3723" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3723" s="1"/>
+    </row>
+    <row r="3724" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3724" s="1"/>
+    </row>
+    <row r="3725" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3725" s="1"/>
+    </row>
+    <row r="3726" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3726" s="1"/>
+    </row>
+    <row r="3727" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3727" s="1"/>
+    </row>
+    <row r="3728" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3728" s="1"/>
+    </row>
+    <row r="3729" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3729" s="1"/>
+    </row>
+    <row r="3730" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3730" s="1"/>
+    </row>
+    <row r="3731" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3731" s="1"/>
+    </row>
+    <row r="3732" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3732" s="1"/>
+    </row>
+    <row r="3733" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3733" s="1"/>
+    </row>
+    <row r="3734" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3734" s="1"/>
+    </row>
+    <row r="3735" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3735" s="1"/>
+    </row>
+    <row r="3736" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3736" s="1"/>
+    </row>
+    <row r="3737" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3737" s="1"/>
+    </row>
+    <row r="3738" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3738" s="1"/>
+    </row>
+    <row r="3739" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3739" s="1"/>
+    </row>
+    <row r="3740" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3740" s="1"/>
+    </row>
+    <row r="3741" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3741" s="1"/>
+    </row>
+    <row r="3742" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3742" s="1"/>
+    </row>
+    <row r="3743" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3743" s="1"/>
+    </row>
+    <row r="3744" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3744" s="1"/>
+    </row>
+    <row r="3745" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3745" s="1"/>
+    </row>
+    <row r="3746" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3746" s="1"/>
+    </row>
+    <row r="3747" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3747" s="1"/>
+    </row>
+    <row r="3748" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3748" s="1"/>
+    </row>
+    <row r="3749" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3749" s="1"/>
+    </row>
+    <row r="3750" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3750" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
